--- a/공동구매_모니터링_템플릿.xlsx
+++ b/공동구매_모니터링_템플릿.xlsx
@@ -2314,7 +2314,7 @@
       <formula1>채널마스터!$A$4:$A$200</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="S4:S500">
-      <formula1>"수동입력,유튜브API,네이버API,기타"</formula1>
+      <formula1>"수동입력,인스타링크 자동입력,유튜브API,네이버API,기타"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
